--- a/Notes/datamapping-ITEMS.xlsx
+++ b/Notes/datamapping-ITEMS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrawford\Desktop\SilverMirror Shortcuts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C4B680C-F452-4F74-B434-05BE539704F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D434945-786B-4DD1-8166-25EFCE96483A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43065" yWindow="-1035" windowWidth="14535" windowHeight="15585" xr2:uid="{58C3F88D-517A-4962-A345-40795FBFBBAA}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{58C3F88D-517A-4962-A345-40795FBFBBAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -600,78 +600,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1004,968 +933,903 @@
   <dimension ref="A1:C164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="1"/>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="1"/>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B39" s="1"/>
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="1"/>
       <c r="C40" s="1"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="1"/>
       <c r="C41" s="1"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B42" s="1"/>
       <c r="C42" s="1"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B43" s="1"/>
       <c r="C43" s="1"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B44" s="1"/>
       <c r="C44" s="1"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B45" s="1"/>
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B46" s="1"/>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B47" s="1"/>
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B48" s="1"/>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="1"/>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="1"/>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B51" s="1"/>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="1"/>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B53" s="1"/>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B54" s="1"/>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="1"/>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="1"/>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B57" s="1"/>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="1"/>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="1"/>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="1"/>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="1"/>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B62" s="1"/>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B63" s="1"/>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B64" s="1"/>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
+      <c r="A81" t="s">
+        <v>164</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B81" t="s">
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="2" t="s">
+      <c r="B138" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B138" t="s">
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
+      <c r="B142" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B142" t="s">
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B153" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A157" s="2" t="s">
+      <c r="B157" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B157" t="s">
-        <v>164</v>
-      </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="B158" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="B159" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="B160" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
         <v>161</v>
       </c>
     </row>

--- a/Notes/datamapping-ITEMS.xlsx
+++ b/Notes/datamapping-ITEMS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D434945-786B-4DD1-8166-25EFCE96483A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688E2207-FD4F-4A27-AD4D-91D2A826BCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{58C3F88D-517A-4962-A345-40795FBFBBAA}"/>
+    <workbookView xWindow="900" yWindow="585" windowWidth="25215" windowHeight="14775" xr2:uid="{58C3F88D-517A-4962-A345-40795FBFBBAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="201">
   <si>
     <t>NO_ITEM</t>
   </si>
@@ -531,13 +531,121 @@
   </si>
   <si>
     <t>evolve</t>
+  </si>
+  <si>
+    <t>kanto</t>
+  </si>
+  <si>
+    <t>kanto (get another in johto?)</t>
+  </si>
+  <si>
+    <t>viridian forest</t>
+  </si>
+  <si>
+    <t>route 5</t>
+  </si>
+  <si>
+    <t>digletts cave</t>
+  </si>
+  <si>
+    <t>rock tunnel</t>
+  </si>
+  <si>
+    <t>pokemon tower</t>
+  </si>
+  <si>
+    <t>celadon city</t>
+  </si>
+  <si>
+    <t>pokemon mansion</t>
+  </si>
+  <si>
+    <t>game corner</t>
+  </si>
+  <si>
+    <t>rocket hideout</t>
+  </si>
+  <si>
+    <t>route 16</t>
+  </si>
+  <si>
+    <t>route 19</t>
+  </si>
+  <si>
+    <t>mr psychics house</t>
+  </si>
+  <si>
+    <t>fighting dojo</t>
+  </si>
+  <si>
+    <t>seafoam islands</t>
+  </si>
+  <si>
+    <t>route 10</t>
+  </si>
+  <si>
+    <t>cerulean cave</t>
+  </si>
+  <si>
+    <t>fast ship first trip</t>
+  </si>
+  <si>
+    <t>held by snorlax</t>
+  </si>
+  <si>
+    <t>route 5 hidden</t>
+  </si>
+  <si>
+    <t>mount moon</t>
+  </si>
+  <si>
+    <t>oaks aide</t>
+  </si>
+  <si>
+    <t>celadon café</t>
+  </si>
+  <si>
+    <t>silph co</t>
+  </si>
+  <si>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>pokegear</t>
+  </si>
+  <si>
+    <t>bike shop</t>
+  </si>
+  <si>
+    <t>shop?</t>
+  </si>
+  <si>
+    <t>gift</t>
+  </si>
+  <si>
+    <t>berry</t>
+  </si>
+  <si>
+    <t>remove?</t>
+  </si>
+  <si>
+    <t>pokemon fan club</t>
+  </si>
+  <si>
+    <t>safari zone</t>
+  </si>
+  <si>
+    <t>appricorn ball</t>
+  </si>
+  <si>
+    <t>dark cave?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,6 +662,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -591,11 +706,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -930,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B84EEE-D36D-4759-9630-508DF0494615}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.85546875" customWidth="1"/>
@@ -947,13 +1063,17 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -965,25 +1085,33 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
@@ -995,73 +1123,97 @@
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
@@ -1073,49 +1225,65 @@
       <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="1"/>
+      <c r="C23" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="1"/>
+      <c r="C24" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="1"/>
+      <c r="C25" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="1"/>
+      <c r="C26" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="1"/>
+      <c r="C27" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="1"/>
+      <c r="C29" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="1"/>
+      <c r="C30" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
@@ -1127,7 +1295,9 @@
       <c r="B32" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="1"/>
+      <c r="C32" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
@@ -1139,13 +1309,17 @@
       <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="1"/>
+      <c r="C34" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="1"/>
+      <c r="C35" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
@@ -1163,127 +1337,169 @@
       <c r="B38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="1"/>
+      <c r="C38" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="1"/>
+      <c r="C39" s="1" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="1"/>
+      <c r="C40" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="1"/>
+      <c r="C42" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C43" s="1"/>
+      <c r="C43" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="1"/>
+      <c r="C44" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C47" s="1"/>
+      <c r="C47" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C49" s="1"/>
+      <c r="C49" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C50" s="1"/>
+      <c r="C50" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="1"/>
+      <c r="C51" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C52" s="1"/>
+      <c r="C52" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C53" s="1"/>
+      <c r="C53" s="1" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C54" s="1"/>
+      <c r="C54" s="1" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C55" s="1"/>
+      <c r="C55" s="1" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C56" s="1"/>
+      <c r="C56" s="1" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C57" s="1"/>
+      <c r="C57" s="1" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C58" s="1"/>
+      <c r="C58" s="1" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
@@ -1295,7 +1511,9 @@
       <c r="B60" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C60" s="1"/>
+      <c r="C60" s="1" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
@@ -1321,87 +1539,114 @@
       </c>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>164</v>
       </c>
@@ -1409,310 +1654,422 @@
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C83" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B87" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C88" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B90" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C92" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B93" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C93" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B94" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C94" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B95" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C97" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C98" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C99" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C100" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C101" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D101" s="3"/>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C102" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C103" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C106" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C107" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C108" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C111" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C112" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C113" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C116" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C118" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C119" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C124" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C126" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C127" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C134" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B135" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C135" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B136" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B137" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C137" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>164</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C138" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B139" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B140" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C140" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>164</v>
       </c>
@@ -1720,77 +2077,98 @@
         <v>149</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B143" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C145" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C146" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C147" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C148" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B149" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C150" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C151" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C152" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B153" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B154" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B156" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>164</v>
       </c>
@@ -1798,17 +2176,23 @@
         <v>154</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C158" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C159" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
         <v>157</v>
       </c>

--- a/Notes/datamapping-ITEMS.xlsx
+++ b/Notes/datamapping-ITEMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B06FE1-4763-4ED2-893E-E62DE0168DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A476F2C0-6574-4BD6-A337-880D5479D625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{58C3F88D-517A-4962-A345-40795FBFBBAA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="292">
   <si>
     <t>NO_ITEM</t>
   </si>
@@ -614,9 +614,6 @@
     <t>mt moon square</t>
   </si>
   <si>
-    <t>else?</t>
-  </si>
-  <si>
     <t>indigo shop</t>
   </si>
   <si>
@@ -900,6 +897,21 @@
   </si>
   <si>
     <t>goldenrod prize</t>
+  </si>
+  <si>
+    <t>lucky number 3</t>
+  </si>
+  <si>
+    <t>lucky number 2</t>
+  </si>
+  <si>
+    <t>lucky number 1</t>
+  </si>
+  <si>
+    <t>lucky number 5</t>
+  </si>
+  <si>
+    <t>lucky number 4</t>
   </si>
 </sst>
 </file>
@@ -1302,22 +1314,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B84EEE-D36D-4759-9630-508DF0494615}">
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="15.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="27" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="4" max="5" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -1325,11 +1337,11 @@
       <c r="C2" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -1338,18 +1350,18 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>4</v>
@@ -1358,7 +1370,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -1367,16 +1379,16 @@
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>6</v>
@@ -1385,7 +1397,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="3" t="s">
         <v>7</v>
@@ -1393,11 +1405,11 @@
       <c r="C9" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>8</v>
@@ -1406,7 +1418,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>96</v>
@@ -1415,7 +1427,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>97</v>
@@ -1424,7 +1436,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>98</v>
@@ -1433,7 +1445,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>99</v>
@@ -1442,22 +1454,22 @@
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1510,8 +1522,8 @@
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D22" t="s">
-        <v>194</v>
+      <c r="D22" s="2" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,7 +1532,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1529,7 +1541,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,7 +1550,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1547,7 +1559,7 @@
         <v>18</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1556,7 +1568,7 @@
         <v>102</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1565,7 +1577,7 @@
         <v>103</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1574,7 +1586,7 @@
         <v>104</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,18 +1595,18 @@
         <v>105</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1603,69 +1615,69 @@
         <v>107</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
         <v>25</v>
@@ -1674,7 +1686,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
         <v>26</v>
@@ -1683,25 +1695,25 @@
         <v>183</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
         <v>108</v>
@@ -1710,7 +1722,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
         <v>109</v>
@@ -1719,40 +1731,40 @@
         <v>183</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1761,7 +1773,7 @@
         <v>29</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1770,7 +1782,7 @@
         <v>30</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1779,7 +1791,7 @@
         <v>31</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1788,7 +1800,7 @@
         <v>32</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1797,7 +1809,7 @@
         <v>33</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1869,7 +1881,10 @@
         <v>116</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1878,7 +1893,7 @@
         <v>117</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1886,8 +1901,8 @@
       <c r="B63" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D63" t="s">
-        <v>194</v>
+      <c r="D63" s="2" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1896,7 +1911,7 @@
         <v>119</v>
       </c>
       <c r="D64" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,10 +1920,10 @@
         <v>39</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D65" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1917,7 +1932,7 @@
         <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1926,7 +1941,7 @@
         <v>41</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1935,7 +1950,7 @@
         <v>42</v>
       </c>
       <c r="D68" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1944,7 +1959,7 @@
         <v>43</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1953,7 +1968,7 @@
         <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1962,23 +1977,23 @@
         <v>45</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D72" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>47</v>
@@ -1998,7 +2013,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>120</v>
@@ -2009,7 +2024,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>121</v>
@@ -2020,7 +2035,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>122</v>
@@ -2031,7 +2046,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>123</v>
@@ -2042,7 +2057,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>124</v>
@@ -2053,7 +2068,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>125</v>
@@ -2062,20 +2077,20 @@
         <v>172</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>50</v>
@@ -2084,9 +2099,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>51</v>
@@ -2095,7 +2110,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
         <v>52</v>
@@ -2104,27 +2119,27 @@
         <v>186</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>55</v>
@@ -2133,7 +2148,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
         <v>56</v>
@@ -2142,7 +2157,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
         <v>57</v>
@@ -2151,9 +2166,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>58</v>
@@ -2162,7 +2177,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1" t="s">
         <v>126</v>
@@ -2171,7 +2186,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
         <v>127</v>
@@ -2180,31 +2195,31 @@
         <v>186</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C94" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
         <v>218</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>130</v>
@@ -2213,7 +2228,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1" t="s">
         <v>131</v>
@@ -2222,9 +2237,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>59</v>
@@ -2233,7 +2248,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1" t="s">
         <v>60</v>
@@ -2242,7 +2257,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1" t="s">
         <v>61</v>
@@ -2251,7 +2266,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1" t="s">
         <v>62</v>
@@ -2260,30 +2275,30 @@
         <v>186</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D101" s="1"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>64</v>
@@ -2292,34 +2307,34 @@
         <v>163</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C104" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>66</v>
       </c>
       <c r="D105" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>67</v>
@@ -2328,9 +2343,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>132</v>
@@ -2339,9 +2354,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>133</v>
@@ -2350,10 +2365,10 @@
         <v>186</v>
       </c>
       <c r="D108" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1" t="s">
         <v>134</v>
@@ -2362,7 +2377,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1" t="s">
         <v>135</v>
@@ -2371,9 +2386,9 @@
         <v>190</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>136</v>
@@ -2382,9 +2397,9 @@
         <v>179</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>137</v>
@@ -2393,7 +2408,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1" t="s">
         <v>160</v>
@@ -2402,21 +2417,21 @@
         <v>170</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>70</v>
@@ -2425,23 +2440,23 @@
         <v>167</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>72</v>
@@ -2450,54 +2465,54 @@
         <v>174</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D120" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D121" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D122" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1" t="s">
         <v>138</v>
       </c>
       <c r="D123" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>139</v>
@@ -2506,18 +2521,21 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1" t="s">
         <v>141</v>
@@ -2526,7 +2544,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1" t="s">
         <v>161</v>
@@ -2535,19 +2553,19 @@
         <v>187</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1" t="s">
         <v>77</v>
@@ -2556,7 +2574,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1" t="s">
         <v>78</v>
@@ -2564,26 +2582,26 @@
       <c r="C131" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D131" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E131" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D133" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1" t="s">
         <v>80</v>
@@ -2592,9 +2610,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>81</v>
@@ -2603,20 +2621,20 @@
         <v>168</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D136" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>83</v>
@@ -2625,31 +2643,31 @@
         <v>177</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>145</v>
       </c>
       <c r="D139" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>146</v>
@@ -2658,12 +2676,12 @@
         <v>178</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>147</v>
@@ -2672,36 +2690,36 @@
         <v>186</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1" t="s">
         <v>149</v>
       </c>
       <c r="D143" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D144" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1" t="s">
         <v>85</v>
@@ -2710,7 +2728,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1" t="s">
         <v>86</v>
@@ -2719,7 +2737,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1" t="s">
         <v>87</v>
@@ -2728,7 +2746,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1" t="s">
         <v>88</v>
@@ -2737,18 +2755,18 @@
         <v>189</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D149" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E149" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1" t="s">
         <v>90</v>
@@ -2757,7 +2775,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1" t="s">
         <v>91</v>
@@ -2766,7 +2784,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1" t="s">
         <v>92</v>
@@ -2775,56 +2793,56 @@
         <v>189</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D153" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D154" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="3" t="s">
         <v>151</v>
       </c>
       <c r="D155" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D156" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>153</v>
@@ -2833,9 +2851,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>154</v>
@@ -2844,7 +2862,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1" t="s">
         <v>155</v>
@@ -2856,7 +2874,7 @@
         <v>156</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -2865,7 +2883,7 @@
         <v>157</v>
       </c>
       <c r="D162" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -2883,18 +2901,18 @@
         <v>159</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>185</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/Notes/datamapping-ITEMS.xlsx
+++ b/Notes/datamapping-ITEMS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A476F2C0-6574-4BD6-A337-880D5479D625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EE3CB6-DD8B-413B-A0EF-07F0C977EE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{58C3F88D-517A-4962-A345-40795FBFBBAA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="296">
   <si>
     <t>NO_ITEM</t>
   </si>
@@ -155,9 +155,6 @@
     <t>GOOD_ROD</t>
   </si>
   <si>
-    <t>RED_SCALE</t>
-  </si>
-  <si>
     <t>SECRETPOTION</t>
   </si>
   <si>
@@ -467,9 +464,6 @@
     <t>EGG_TICKET</t>
   </si>
   <si>
-    <t>LOST_ITEM</t>
-  </si>
-  <si>
     <t>BASEMENT_KEY</t>
   </si>
   <si>
@@ -629,15 +623,9 @@
     <t>vending</t>
   </si>
   <si>
-    <t>mary?</t>
-  </si>
-  <si>
     <t>celadon prize</t>
   </si>
   <si>
-    <t>replace?-gold scale, magikarp</t>
-  </si>
-  <si>
     <t>unused</t>
   </si>
   <si>
@@ -842,9 +830,6 @@
     <t>wild farfetchd (2%)</t>
   </si>
   <si>
-    <t>kanto? fast ship?</t>
-  </si>
-  <si>
     <t>wild paras (23%)</t>
   </si>
   <si>
@@ -875,9 +860,6 @@
     <t>dark cave</t>
   </si>
   <si>
-    <t>where?</t>
-  </si>
-  <si>
     <t>underground shop</t>
   </si>
   <si>
@@ -912,6 +894,36 @@
   </si>
   <si>
     <t>lucky number 4</t>
+  </si>
+  <si>
+    <t>fast ship</t>
+  </si>
+  <si>
+    <t>bill's family's house</t>
+  </si>
+  <si>
+    <t>GOLD_SCALE</t>
+  </si>
+  <si>
+    <t>route 30</t>
+  </si>
+  <si>
+    <t>flower shop</t>
+  </si>
+  <si>
+    <t>buena</t>
+  </si>
+  <si>
+    <t>CARD_KEY_R</t>
+  </si>
+  <si>
+    <t>radio tower</t>
+  </si>
+  <si>
+    <t>mary</t>
+  </si>
+  <si>
+    <t>young chris</t>
   </si>
 </sst>
 </file>
@@ -1335,10 +1347,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1347,18 +1359,18 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>197</v>
+      <c r="C4" s="2" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1367,7 +1379,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1376,16 +1388,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1394,7 +1406,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1403,10 +1415,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1415,207 +1427,207 @@
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="C31" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1624,7 +1636,7 @@
         <v>19</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1633,7 +1645,7 @@
         <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1642,21 +1654,21 @@
         <v>21</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1665,7 +1677,7 @@
         <v>23</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1674,7 +1686,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1683,7 +1695,7 @@
         <v>25</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1692,7 +1704,7 @@
         <v>26</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1701,7 +1713,7 @@
         <v>27</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1710,61 +1722,61 @@
         <v>28</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1773,7 +1785,7 @@
         <v>29</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1782,7 +1794,7 @@
         <v>30</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1791,7 +1803,7 @@
         <v>31</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1800,7 +1812,7 @@
         <v>32</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1809,7 +1821,7 @@
         <v>33</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1818,7 +1830,7 @@
         <v>34</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1827,7 +1839,7 @@
         <v>35</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1836,7 +1848,7 @@
         <v>36</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1845,7 +1857,7 @@
         <v>37</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1854,1065 +1866,1074 @@
         <v>38</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D65" t="s">
-        <v>199</v>
+        <v>288</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D66" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D68" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D69" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D70" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D72" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D101" s="1"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D105" t="s">
-        <v>268</v>
+        <v>65</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D108" t="s">
-        <v>279</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D120" t="s">
-        <v>280</v>
+        <v>73</v>
+      </c>
+      <c r="C120" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D121" t="s">
-        <v>280</v>
+        <v>74</v>
+      </c>
+      <c r="C121" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D122" t="s">
-        <v>280</v>
+        <v>75</v>
+      </c>
+      <c r="C122" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D123" t="s">
-        <v>280</v>
+        <v>137</v>
+      </c>
+      <c r="C123" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>291</v>
+        <v>139</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1" t="s">
-        <v>143</v>
+        <v>292</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D133" t="s">
-        <v>281</v>
+        <v>78</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D136" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D139" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D143" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D144" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D153" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D154" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D155" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="D156" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D162" t="s">
-        <v>242</v>
+        <v>155</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/Notes/datamapping-ITEMS.xlsx
+++ b/Notes/datamapping-ITEMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EE3CB6-DD8B-413B-A0EF-07F0C977EE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE219CA-A6C2-4F73-8C72-657F6BE3DEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{58C3F88D-517A-4962-A345-40795FBFBBAA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="297">
   <si>
     <t>NO_ITEM</t>
   </si>
@@ -464,9 +464,6 @@
     <t>EGG_TICKET</t>
   </si>
   <si>
-    <t>BASEMENT_KEY</t>
-  </si>
-  <si>
     <t>DRAGON_FANG</t>
   </si>
   <si>
@@ -866,12 +863,6 @@
     <t>goldenrod</t>
   </si>
   <si>
-    <t>schuckle does it?</t>
-  </si>
-  <si>
-    <t>cerulean cave?</t>
-  </si>
-  <si>
     <t>something fancy, make it reusable?</t>
   </si>
   <si>
@@ -924,6 +915,18 @@
   </si>
   <si>
     <t>young chris</t>
+  </si>
+  <si>
+    <t>dragon's den elders building</t>
+  </si>
+  <si>
+    <t>LIFT_KEY</t>
+  </si>
+  <si>
+    <t>shuckle</t>
+  </si>
+  <si>
+    <t>after mewtwo</t>
   </si>
 </sst>
 </file>
@@ -1347,10 +1350,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1359,18 +1362,18 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1379,7 +1382,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1388,7 +1391,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1397,7 +1400,7 @@
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1406,7 +1409,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1415,10 +1418,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1427,7 +1430,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1436,7 +1439,7 @@
         <v>95</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1445,7 +1448,7 @@
         <v>96</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1454,7 +1457,7 @@
         <v>97</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1463,7 +1466,7 @@
         <v>98</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1472,7 +1475,7 @@
         <v>99</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1481,7 +1484,7 @@
         <v>100</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1490,7 +1493,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1499,7 +1502,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1508,7 +1511,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1517,7 +1520,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1526,7 +1529,7 @@
         <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1535,7 +1538,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1544,7 +1547,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1553,7 +1556,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1562,7 +1565,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1571,7 +1574,7 @@
         <v>18</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1580,7 +1583,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1589,7 +1592,7 @@
         <v>102</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1598,7 +1601,7 @@
         <v>103</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1607,18 +1610,18 @@
         <v>104</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1627,7 +1630,7 @@
         <v>106</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1636,7 +1639,7 @@
         <v>19</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1645,7 +1648,7 @@
         <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1654,21 +1657,21 @@
         <v>21</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1677,7 +1680,7 @@
         <v>23</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1686,7 +1689,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1695,7 +1698,7 @@
         <v>25</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1704,7 +1707,7 @@
         <v>26</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1713,7 +1716,7 @@
         <v>27</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1722,7 +1725,7 @@
         <v>28</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1731,7 +1734,7 @@
         <v>107</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1740,7 +1743,7 @@
         <v>108</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1749,7 +1752,7 @@
         <v>109</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1758,7 +1761,7 @@
         <v>110</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1767,7 +1770,7 @@
         <v>111</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1776,7 +1779,7 @@
         <v>112</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1785,7 +1788,7 @@
         <v>29</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1794,7 +1797,7 @@
         <v>30</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1803,7 +1806,7 @@
         <v>31</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,7 +1815,7 @@
         <v>32</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1821,7 +1824,7 @@
         <v>33</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1830,7 +1833,7 @@
         <v>34</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1839,7 +1842,7 @@
         <v>35</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1848,7 +1851,7 @@
         <v>36</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1857,7 +1860,7 @@
         <v>37</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1866,7 +1869,7 @@
         <v>38</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1875,7 +1878,7 @@
         <v>113</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,7 +1887,7 @@
         <v>114</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1893,10 +1896,10 @@
         <v>115</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,7 +1908,7 @@
         <v>116</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1914,7 +1917,7 @@
         <v>117</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1923,16 +1926,16 @@
         <v>118</v>
       </c>
       <c r="D64" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1941,7 +1944,7 @@
         <v>39</v>
       </c>
       <c r="D66" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1950,7 +1953,7 @@
         <v>40</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1959,7 +1962,7 @@
         <v>41</v>
       </c>
       <c r="D68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1968,7 +1971,7 @@
         <v>42</v>
       </c>
       <c r="D69" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1977,7 +1980,7 @@
         <v>43</v>
       </c>
       <c r="D70" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1986,29 +1989,29 @@
         <v>44</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D72" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2017,106 +2020,106 @@
         <v>47</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>122</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2125,7 +2128,7 @@
         <v>51</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2134,7 +2137,7 @@
         <v>52</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2143,21 +2146,21 @@
         <v>53</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2166,7 +2169,7 @@
         <v>55</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2175,18 +2178,18 @@
         <v>56</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2195,7 +2198,7 @@
         <v>125</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2204,40 +2207,40 @@
         <v>126</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2246,18 +2249,18 @@
         <v>130</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2266,7 +2269,7 @@
         <v>59</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2275,7 +2278,7 @@
         <v>60</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2284,97 +2287,97 @@
         <v>61</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>273</v>
+      <c r="C101" s="2" t="s">
+        <v>272</v>
       </c>
       <c r="D101" s="1"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C104" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>286</v>
+      <c r="C105" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2383,7 +2386,7 @@
         <v>133</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -2392,38 +2395,38 @@
         <v>134</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2432,7 +2435,7 @@
         <v>67</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2440,44 +2443,44 @@
       <c r="B115" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>291</v>
+      <c r="C115" s="2" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -2486,7 +2489,7 @@
         <v>72</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -2495,7 +2498,7 @@
         <v>73</v>
       </c>
       <c r="C120" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -2504,7 +2507,7 @@
         <v>74</v>
       </c>
       <c r="C121" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -2513,7 +2516,7 @@
         <v>75</v>
       </c>
       <c r="C122" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -2522,32 +2525,32 @@
         <v>137</v>
       </c>
       <c r="C123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -2556,16 +2559,16 @@
         <v>140</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -2573,14 +2576,17 @@
       <c r="B128" s="1" t="s">
         <v>141</v>
       </c>
+      <c r="D128" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -2589,7 +2595,7 @@
         <v>76</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -2598,16 +2604,19 @@
         <v>77</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1" t="s">
-        <v>142</v>
+        <v>294</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -2616,7 +2625,7 @@
         <v>78</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -2625,116 +2634,116 @@
         <v>79</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D136" t="s">
-        <v>276</v>
+      <c r="C136" s="2" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D139" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D143" t="s">
-        <v>277</v>
+        <v>146</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D144" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -2743,7 +2752,7 @@
         <v>84</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -2752,7 +2761,7 @@
         <v>85</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -2761,7 +2770,7 @@
         <v>86</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -2770,18 +2779,18 @@
         <v>87</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -2790,7 +2799,7 @@
         <v>89</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -2799,7 +2808,7 @@
         <v>90</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -2808,7 +2817,7 @@
         <v>91</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -2817,7 +2826,7 @@
         <v>92</v>
       </c>
       <c r="D153" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -2826,114 +2835,114 @@
         <v>93</v>
       </c>
       <c r="D154" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D155" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D156" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>290</v>
+        <v>152</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D165" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -2941,5 +2950,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>